--- a/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_clap_bert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_clap_bert-base-uncased_zeroshot.xlsx
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.340382641999895</v>
+        <v>28.0341141630015</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002113460880666632</v>
+        <v>0.009344704721000501</v>
       </c>
     </row>
   </sheetData>
